--- a/artfynd/A 34818-2019 artfynd.xlsx
+++ b/artfynd/A 34818-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34818-2019 artfynd.xlsx
+++ b/artfynd/A 34818-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1290,6 +1290,120 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120206957</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57226</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Frö, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>550757</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6485811</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lillkyrka</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Louise Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Louise Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34818-2019 artfynd.xlsx
+++ b/artfynd/A 34818-2019 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>120206957</v>
       </c>
       <c r="B7" t="n">
-        <v>57226</v>
+        <v>57236</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
